--- a/course-design-2/outputs/tables/ch7/22_model_comparison.xlsx
+++ b/course-design-2/outputs/tables/ch7/22_model_comparison.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_数据划分" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_特征维度" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Ridge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RandomForest" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_CatBoost" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Boosting" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Validation比较" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Test最终结果" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_预测残差" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_技能阈值选择" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_文本维度选择" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_门禁" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="01_数据划分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_特征维度" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_Baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_Ridge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_RandomForest" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_CatBoost" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_Boosting" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_Validation比较" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_Test最终结果" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_预测残差" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="12_技能阈值选择" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="13_文本维度选择" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_门禁" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,31 +792,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.335506</v>
+        <v>35.651021</v>
       </c>
       <c r="C2" t="n">
-        <v>64.623479</v>
+        <v>65.020978</v>
       </c>
       <c r="D2" t="n">
-        <v>0.584606</v>
+        <v>0.57948</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7322</v>
+        <v>-1.8555</v>
       </c>
       <c r="G2" t="n">
-        <v>64.6147</v>
+        <v>65.0091</v>
       </c>
       <c r="H2" t="n">
-        <v>-57.1932</v>
+        <v>-58.2148</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.5752</v>
+        <v>-4.2174</v>
       </c>
       <c r="J2" t="n">
-        <v>46.5589</v>
+        <v>47.6083</v>
       </c>
       <c r="K2" t="n">
         <v>0.050605</v>
@@ -830,7 +830,7 @@
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>53.447</v>
+        <v>54.03</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -855,7 +855,7 @@
         <v>290</v>
       </c>
       <c r="O3" t="n">
-        <v>32.7858</v>
+        <v>29.8141</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>45.6739</v>
+        <v>44.1704</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -891,7 +891,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>26.983</v>
+        <v>24.7732</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>43.3996</v>
+        <v>43.2211</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -920,14 +920,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>15人以下</t>
+          <t>150-500人</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>57</v>
+        <v>241</v>
       </c>
       <c r="O5" t="n">
-        <v>35.9745</v>
+        <v>28.8682</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>42.0774</v>
+        <v>41.982</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -956,14 +956,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>150-500人</t>
+          <t>50-150人</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="O6" t="n">
-        <v>27.3491</v>
+        <v>27.0113</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>40.9318</v>
+        <v>40.1732</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -992,14 +992,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>50-150人</t>
+          <t>15人以下</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>57</v>
       </c>
       <c r="O7" t="n">
-        <v>26.5116</v>
+        <v>31.0697</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>32.5497</v>
+        <v>32.7175</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>232</v>
       </c>
       <c r="O8" t="n">
-        <v>22.6242</v>
+        <v>24.6525</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>27.3094</v>
+        <v>27.5938</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>1099</v>
       </c>
       <c r="O9" t="n">
-        <v>18.218</v>
+        <v>18.6493</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>52.6618</v>
+        <v>53.5022</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
         <v>158</v>
       </c>
       <c r="O10" t="n">
-        <v>37.275</v>
+        <v>33.8417</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>37.618</v>
+        <v>37.685</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
         <v>299</v>
       </c>
       <c r="O11" t="n">
-        <v>22.7282</v>
+        <v>24.1192</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>33.4648</v>
+        <v>33.7446</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         <v>1617</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5768</v>
+        <v>21.9927</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>32.8174</v>
+        <v>33.5874</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
         <v>157</v>
       </c>
       <c r="O13" t="n">
-        <v>21.1392</v>
+        <v>23.8537</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>60.9339</v>
+        <v>62.6782</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
         <v>237</v>
       </c>
       <c r="O14" t="n">
-        <v>32.5675</v>
+        <v>34.2434</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>57.7823</v>
+        <v>60.1151</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1280,14 +1280,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>运维/技术支持</t>
+          <t>前端开发</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="O15" t="n">
-        <v>30.1488</v>
+        <v>38.3122</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>57.5152</v>
+        <v>58.4255</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>前端开发</t>
+          <t>运维/技术支持</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>141</v>
+        <v>250</v>
       </c>
       <c r="O16" t="n">
-        <v>33.8371</v>
+        <v>30.1724</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>56.3754</v>
+        <v>57.7502</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
         <v>363</v>
       </c>
       <c r="O17" t="n">
-        <v>35.4081</v>
+        <v>34.6684</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>55.6234</v>
+        <v>56.7403</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -1388,14 +1388,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>499</v>
+        <v>205</v>
       </c>
       <c r="O18" t="n">
-        <v>32.5296</v>
+        <v>30.692</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>55.5526</v>
+        <v>56.3301</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -1424,14 +1424,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>499</v>
       </c>
       <c r="O19" t="n">
-        <v>29.7517</v>
+        <v>33.027</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>49.3472</v>
+        <v>50.3407</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
         <v>437</v>
       </c>
       <c r="O20" t="n">
-        <v>28.4366</v>
+        <v>30.3556</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>34.1592</v>
+        <v>34.5951</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1503,7 +1503,7 @@
         <v>164</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3439</v>
+        <v>22.524</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>33.5452</v>
+        <v>34.3769</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1532,14 +1532,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>技术管理</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="O22" t="n">
-        <v>28.5191</v>
+        <v>28.1928</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>32.4563</v>
+        <v>34.0196</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1568,14 +1568,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>技术管理</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="O23" t="n">
-        <v>25.1328</v>
+        <v>27.6413</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>29.4966</v>
+        <v>29.3821</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
         <v>1493</v>
       </c>
       <c r="O24" t="n">
-        <v>20.4918</v>
+        <v>20.4702</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>29.1703</v>
+        <v>29.3466</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
         <v>933</v>
       </c>
       <c r="O25" t="n">
-        <v>20.3111</v>
+        <v>20.8215</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>57.2473</v>
+        <v>57.0826</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
         <v>149</v>
       </c>
       <c r="O26" t="n">
-        <v>32.3671</v>
+        <v>31.0697</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>36.3554</v>
+        <v>36.8899</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
         <v>699</v>
       </c>
       <c r="O27" t="n">
-        <v>22.4045</v>
+        <v>21.9927</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>34.1864</v>
+        <v>35.3218</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="O28" t="n">
-        <v>22.2549</v>
+        <v>32.0965</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>32.2856</v>
+        <v>33.7521</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1784,14 +1784,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="O29" t="n">
-        <v>28.7945</v>
+        <v>24.6849</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>31.8787</v>
+        <v>31.8696</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
         <v>641</v>
       </c>
       <c r="O30" t="n">
-        <v>22.782</v>
+        <v>23.5366</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>28.9038</v>
+        <v>28.6036</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1856,14 +1856,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O31" t="n">
-        <v>24.6468</v>
+        <v>17.5267</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>28.4634</v>
+        <v>28.5987</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
         <v>161</v>
       </c>
       <c r="O32" t="n">
-        <v>20.7984</v>
+        <v>22.0296</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>27.7314</v>
+        <v>28.4153</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1928,14 +1928,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="O33" t="n">
-        <v>16.0163</v>
+        <v>26.1271</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>27.1987</v>
+        <v>28.1975</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
-        <v>22.7484</v>
+        <v>25.5944</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>61.9692</v>
+        <v>62.6642</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
         <v>426</v>
       </c>
       <c r="O35" t="n">
-        <v>36.8443</v>
+        <v>40.125</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>38.9929</v>
+        <v>39.6206</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
         <v>474</v>
       </c>
       <c r="O36" t="n">
-        <v>28.5607</v>
+        <v>29.2978</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>29.6516</v>
+        <v>29.2769</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>464</v>
       </c>
       <c r="O37" t="n">
-        <v>21.9301</v>
+        <v>21.378</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>23.731</v>
+        <v>24.2556</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
         <v>439</v>
       </c>
       <c r="O38" t="n">
-        <v>17.0952</v>
+        <v>18.452</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>22.8987</v>
+        <v>23.0254</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
         <v>430</v>
       </c>
       <c r="O39" t="n">
-        <v>15.2992</v>
+        <v>16.6278</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.3</v>
+        <v>12</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>15.1</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>15.1</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>15.1</v>
+        <v>11.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2436,13 +2436,13 @@
         <v>320</v>
       </c>
       <c r="C2" t="n">
-        <v>37.895056</v>
+        <v>37.947826</v>
       </c>
       <c r="D2" t="n">
-        <v>73.830613</v>
+        <v>74.068512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5418500000000001</v>
+        <v>0.538893</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2463,13 +2463,13 @@
         <v>336</v>
       </c>
       <c r="C3" t="n">
-        <v>38.57584</v>
+        <v>38.572288</v>
       </c>
       <c r="D3" t="n">
-        <v>75.125524</v>
+        <v>74.96394600000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.525638</v>
+        <v>0.527676</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2490,13 +2490,13 @@
         <v>368</v>
       </c>
       <c r="C4" t="n">
-        <v>39.401318</v>
+        <v>39.515381</v>
       </c>
       <c r="D4" t="n">
-        <v>76.091577</v>
+        <v>75.668194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.51336</v>
+        <v>0.51876</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>按 validation MAE 选出主模型 LightGBM（36.088217）；排序前 3：LightGBM、CatBoost、RandomForest；选择只用 train/validation</t>
+          <t>按 validation MAE 选出主模型 LightGBM（36.206167）；排序前 3：LightGBM、CatBoost、RandomForest；选择只用 train/validation</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>test 仅在锁定配置后评估一次（n = 2,233，MAE 35.335506），技能阈值/文本维度/超参数/模型族均在 train+validation 上确定，未据 test 调整</t>
+          <t>test 仅在锁定配置后评估一次（n = 2,233，MAE 35.651021），技能阈值/文本维度/超参数/模型族均在 train+validation 上确定，未据 test 调整</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>阈值 = 100（train 频率），口径 ALL_USABLE</t>
+          <t>阈值 = 100（train 频率），统计范围 ALL_USABLE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>16.3</v>
+        <v>12</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>15.1</v>
+        <v>11.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>15.1</v>
+        <v>11.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>15.1</v>
+        <v>11.8</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -3158,13 +3158,13 @@
         <v>320</v>
       </c>
       <c r="I12" t="n">
-        <v>37.895056</v>
+        <v>37.947826</v>
       </c>
       <c r="J12" t="n">
-        <v>73.830613</v>
+        <v>74.068512</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5418500000000001</v>
+        <v>0.538893</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         <v>336</v>
       </c>
       <c r="I13" t="n">
-        <v>38.57584</v>
+        <v>38.572288</v>
       </c>
       <c r="J13" t="n">
-        <v>75.125524</v>
+        <v>74.96394600000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.525638</v>
+        <v>0.527676</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -3234,13 +3234,13 @@
         <v>368</v>
       </c>
       <c r="I14" t="n">
-        <v>39.401318</v>
+        <v>39.515381</v>
       </c>
       <c r="J14" t="n">
-        <v>76.091577</v>
+        <v>75.668194</v>
       </c>
       <c r="K14" t="n">
-        <v>0.51336</v>
+        <v>0.51876</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.522012</v>
+        <v>45.525327</v>
       </c>
       <c r="D2" t="n">
-        <v>85.260366</v>
+        <v>85.262733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.389017</v>
+        <v>0.388983</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45.487769</v>
+        <v>45.487404</v>
       </c>
       <c r="D3" t="n">
-        <v>85.26552</v>
+        <v>85.26552100000001</v>
       </c>
       <c r="E3" t="n">
         <v>0.388943</v>
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45.385857</v>
+        <v>45.384395</v>
       </c>
       <c r="D4" t="n">
-        <v>85.495599</v>
+        <v>85.49479599999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.385641</v>
+        <v>0.385652</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.491613</v>
+        <v>45.491437</v>
       </c>
       <c r="D5" t="n">
-        <v>86.864029</v>
+        <v>86.86393700000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.365817</v>
+        <v>0.365818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3582,13 +3582,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.895056</v>
+        <v>37.947826</v>
       </c>
       <c r="D2" t="n">
-        <v>73.830613</v>
+        <v>74.068512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5418500000000001</v>
+        <v>0.538893</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3608,13 +3608,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.599681</v>
+        <v>40.526569</v>
       </c>
       <c r="D3" t="n">
-        <v>79.94751100000001</v>
+        <v>79.95421899999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.462789</v>
+        <v>0.462699</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.770234</v>
+        <v>39.013314</v>
       </c>
       <c r="D4" t="n">
-        <v>74.337681</v>
+        <v>74.564498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.535535</v>
+        <v>0.5326959999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.979075</v>
+        <v>40.960824</v>
       </c>
       <c r="D5" t="n">
-        <v>80.340462</v>
+        <v>80.26367500000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.457495</v>
+        <v>0.458532</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38.315285</v>
+        <v>38.704519</v>
       </c>
       <c r="D2" t="n">
-        <v>70.21646200000001</v>
+        <v>70.436943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.585607</v>
+        <v>0.583</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.678336</v>
+        <v>36.677215</v>
       </c>
       <c r="D3" t="n">
-        <v>68.642066</v>
+        <v>68.938822</v>
       </c>
       <c r="E3" t="n">
-        <v>0.603981</v>
+        <v>0.60055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.95015</v>
+        <v>36.815171</v>
       </c>
       <c r="D2" t="n">
-        <v>70.219453</v>
+        <v>70.748233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.585571</v>
+        <v>0.579306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3856,13 +3856,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="D3" t="n">
-        <v>69.294882</v>
+        <v>69.574967</v>
       </c>
       <c r="E3" t="n">
-        <v>0.596413</v>
+        <v>0.593144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.217811</v>
+        <v>37.065414</v>
       </c>
       <c r="D4" t="n">
-        <v>70.950033</v>
+        <v>70.757306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5769030000000001</v>
+        <v>0.579198</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="D2" t="n">
-        <v>69.294882</v>
+        <v>69.574967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.596413</v>
+        <v>0.593144</v>
       </c>
       <c r="F2" t="n">
         <v>320</v>
@@ -3998,13 +3998,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.678336</v>
+        <v>36.677215</v>
       </c>
       <c r="D3" t="n">
-        <v>68.642066</v>
+        <v>68.938822</v>
       </c>
       <c r="E3" t="n">
-        <v>0.603981</v>
+        <v>0.60055</v>
       </c>
       <c r="F3" t="n">
         <v>320</v>
@@ -4032,13 +4032,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.895056</v>
+        <v>37.947826</v>
       </c>
       <c r="D4" t="n">
-        <v>73.830613</v>
+        <v>74.068512</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5418500000000001</v>
+        <v>0.538893</v>
       </c>
       <c r="F4" t="n">
         <v>320</v>
@@ -4066,13 +4066,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.385857</v>
+        <v>45.384395</v>
       </c>
       <c r="D5" t="n">
-        <v>85.495599</v>
+        <v>85.49479599999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.385641</v>
+        <v>0.385652</v>
       </c>
       <c r="F5" t="n">
         <v>320</v>
@@ -4180,13 +4180,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.731547</v>
+        <v>43.731102</v>
       </c>
       <c r="C2" t="n">
-        <v>77.229775</v>
+        <v>77.230745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.406734</v>
+        <v>0.406719</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -4209,13 +4209,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.738923</v>
+        <v>36.875829</v>
       </c>
       <c r="C3" t="n">
-        <v>68.538259</v>
+        <v>68.322874</v>
       </c>
       <c r="D3" t="n">
-        <v>0.532753</v>
+        <v>0.535686</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.275629</v>
+        <v>36.34304</v>
       </c>
       <c r="C4" t="n">
-        <v>64.46742399999999</v>
+        <v>64.751227</v>
       </c>
       <c r="D4" t="n">
-        <v>0.586609</v>
+        <v>0.582962</v>
       </c>
       <c r="E4" t="n">
         <v>2233</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="C5" t="n">
-        <v>66.307726</v>
+        <v>66.191014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.562671</v>
+        <v>0.564209</v>
       </c>
       <c r="E5" t="n">
         <v>2233</v>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.335506</v>
+        <v>35.651021</v>
       </c>
       <c r="C7" t="n">
-        <v>64.623479</v>
+        <v>65.020978</v>
       </c>
       <c r="D7" t="n">
-        <v>0.584606</v>
+        <v>0.57948</v>
       </c>
       <c r="E7" t="n">
         <v>2233</v>

--- a/course-design-2/outputs/tables/ch7/22_model_comparison.xlsx
+++ b/course-design-2/outputs/tables/ch7/22_model_comparison.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_数据划分" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_特征维度" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_Ridge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_RandomForest" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_CatBoost" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_Boosting" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_Validation比较" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_Test最终结果" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_预测残差" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="12_技能阈值选择" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="13_文本维度选择" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="11_门禁" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_数据划分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_特征维度" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Ridge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RandomForest" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_CatBoost" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Boosting" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Validation比较" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Test最终结果" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_预测残差" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_技能阈值选择" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_文本维度选择" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_门禁" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,8 +529,6 @@
       <c r="I2" t="n">
         <v>1750</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,8 +562,6 @@
       <c r="I3" t="n">
         <v>1750</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,8 +595,6 @@
       <c r="I4" t="n">
         <v>1500</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -616,12 +610,6 @@
       <c r="C5" t="n">
         <v>10521</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>2453</v>
       </c>
@@ -645,12 +633,6 @@
       <c r="C6" t="n">
         <v>2674</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>526</v>
       </c>
@@ -674,12 +656,6 @@
       <c r="C7" t="n">
         <v>1688</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>526</v>
       </c>
@@ -792,55 +768,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.651021</v>
+        <v>35.335506</v>
       </c>
       <c r="C2" t="n">
-        <v>65.020978</v>
+        <v>64.623479</v>
       </c>
       <c r="D2" t="n">
-        <v>0.57948</v>
+        <v>0.584606</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8555</v>
+        <v>-1.7322</v>
       </c>
       <c r="G2" t="n">
-        <v>65.0091</v>
+        <v>64.6147</v>
       </c>
       <c r="H2" t="n">
-        <v>-58.2148</v>
+        <v>-57.1932</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.2174</v>
+        <v>-3.5752</v>
       </c>
       <c r="J2" t="n">
-        <v>47.6083</v>
+        <v>46.5589</v>
       </c>
       <c r="K2" t="n">
         <v>0.050605</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>53.447</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>公司规模</t>
@@ -855,7 +816,7 @@
         <v>290</v>
       </c>
       <c r="O3" t="n">
-        <v>29.8141</v>
+        <v>32.7858</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -864,19 +825,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>44.1704</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>45.6739</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>公司规模</t>
@@ -891,7 +842,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>24.7732</v>
+        <v>26.983</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,19 +851,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>43.2211</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>43.3996</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>公司规模</t>
@@ -920,107 +861,77 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>15人以下</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>57</v>
+      </c>
+      <c r="O5" t="n">
+        <v>35.9745</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>42.0774</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>公司规模</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>150-500人</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N6" t="n">
         <v>241</v>
       </c>
-      <c r="O5" t="n">
-        <v>28.8682</v>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="O6" t="n">
+        <v>27.3491</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
-        <v>41.982</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="n">
+        <v>40.9318</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>公司规模</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>50-150人</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="N7" t="n">
         <v>210</v>
       </c>
-      <c r="O6" t="n">
-        <v>27.0113</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="O7" t="n">
+        <v>26.5116</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="n">
-        <v>40.1732</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>公司规模</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>15人以下</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>57</v>
-      </c>
-      <c r="O7" t="n">
-        <v>31.0697</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>32.7175</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>32.5497</v>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>公司规模</t>
@@ -1035,7 +946,7 @@
         <v>232</v>
       </c>
       <c r="O8" t="n">
-        <v>24.6525</v>
+        <v>22.6242</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1044,19 +955,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>27.5938</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>27.3094</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>公司规模</t>
@@ -1071,7 +972,7 @@
         <v>1099</v>
       </c>
       <c r="O9" t="n">
-        <v>18.6493</v>
+        <v>18.218</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1080,19 +981,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>53.5022</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>52.6618</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>学历要求</t>
@@ -1107,7 +998,7 @@
         <v>158</v>
       </c>
       <c r="O10" t="n">
-        <v>33.8417</v>
+        <v>37.275</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1116,19 +1007,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>37.685</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>37.618</v>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>学历要求</t>
@@ -1143,7 +1024,7 @@
         <v>299</v>
       </c>
       <c r="O11" t="n">
-        <v>24.1192</v>
+        <v>22.7282</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1152,19 +1033,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>33.7446</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>33.4648</v>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>学历要求</t>
@@ -1179,7 +1050,7 @@
         <v>1617</v>
       </c>
       <c r="O12" t="n">
-        <v>21.9927</v>
+        <v>21.5768</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1188,19 +1059,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>33.5874</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+        <v>32.8174</v>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>学历要求</t>
@@ -1215,7 +1076,7 @@
         <v>157</v>
       </c>
       <c r="O13" t="n">
-        <v>23.8537</v>
+        <v>21.1392</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1224,19 +1085,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>62.6782</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>60.9339</v>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1251,7 +1102,7 @@
         <v>237</v>
       </c>
       <c r="O14" t="n">
-        <v>34.2434</v>
+        <v>32.5675</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1260,19 +1111,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>60.1151</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>57.7823</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1280,71 +1121,51 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>运维/技术支持</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>250</v>
+      </c>
+      <c r="O15" t="n">
+        <v>30.1488</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>57.5152</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>岗位大类</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>前端开发</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>141</v>
       </c>
-      <c r="O15" t="n">
-        <v>38.3122</v>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="O16" t="n">
+        <v>33.8371</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
-        <v>58.4255</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>岗位大类</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>运维/技术支持</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30.1724</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>57.7502</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+        <v>56.3754</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1359,7 +1180,7 @@
         <v>363</v>
       </c>
       <c r="O17" t="n">
-        <v>34.6684</v>
+        <v>35.4081</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1368,19 +1189,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>56.7403</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>55.6234</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1388,71 +1199,51 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>人工智能</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>499</v>
+      </c>
+      <c r="O18" t="n">
+        <v>32.5296</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>55.5526</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>岗位大类</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>205</v>
       </c>
-      <c r="O18" t="n">
-        <v>30.692</v>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="O19" t="n">
+        <v>29.7517</v>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
-        <v>56.3301</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>岗位大类</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>人工智能</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>499</v>
-      </c>
-      <c r="O19" t="n">
-        <v>33.027</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>50.3407</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>49.3472</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1467,7 +1258,7 @@
         <v>437</v>
       </c>
       <c r="O20" t="n">
-        <v>30.3556</v>
+        <v>28.4366</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1476,19 +1267,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>34.5951</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>34.1592</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1503,7 +1284,7 @@
         <v>164</v>
       </c>
       <c r="O21" t="n">
-        <v>22.524</v>
+        <v>19.3439</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1512,19 +1293,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>34.3769</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+        <v>33.5452</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1532,71 +1303,51 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>游戏</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>120</v>
+      </c>
+      <c r="O22" t="n">
+        <v>28.5191</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>32.4563</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>岗位大类</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>技术管理</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>90</v>
       </c>
-      <c r="O22" t="n">
-        <v>28.1928</v>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="O23" t="n">
+        <v>25.1328</v>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
-        <v>34.0196</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>岗位大类</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>120</v>
-      </c>
-      <c r="O23" t="n">
-        <v>27.6413</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>29.3821</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+        <v>29.4966</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1611,7 +1362,7 @@
         <v>1493</v>
       </c>
       <c r="O24" t="n">
-        <v>20.4702</v>
+        <v>20.4918</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1620,19 +1371,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>29.3466</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+        <v>29.1703</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>岗位大类</t>
@@ -1647,7 +1388,7 @@
         <v>933</v>
       </c>
       <c r="O25" t="n">
-        <v>20.8215</v>
+        <v>20.3111</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1656,19 +1397,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>57.0826</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+        <v>57.2473</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1683,7 +1414,7 @@
         <v>149</v>
       </c>
       <c r="O26" t="n">
-        <v>31.0697</v>
+        <v>32.3671</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -1692,19 +1423,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>36.8899</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+        <v>36.3554</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1719,7 +1440,7 @@
         <v>699</v>
       </c>
       <c r="O27" t="n">
-        <v>21.9927</v>
+        <v>22.4045</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -1728,19 +1449,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>35.3218</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+        <v>34.1864</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1748,71 +1459,51 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>97</v>
+      </c>
+      <c r="O28" t="n">
+        <v>22.2549</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>32.2856</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>工作城市_规范</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="N29" t="n">
         <v>47</v>
       </c>
-      <c r="O28" t="n">
-        <v>32.0965</v>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="O29" t="n">
+        <v>28.7945</v>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
-        <v>33.7521</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>工作城市_规范</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>97</v>
-      </c>
-      <c r="O29" t="n">
-        <v>24.6849</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>31.8696</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+        <v>31.8787</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1827,7 +1518,7 @@
         <v>641</v>
       </c>
       <c r="O30" t="n">
-        <v>23.5366</v>
+        <v>22.782</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -1836,19 +1527,9 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>28.6036</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+        <v>28.9038</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1856,14 +1537,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O31" t="n">
-        <v>17.5267</v>
+        <v>24.6468</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -1872,19 +1553,9 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>28.5987</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+        <v>28.4634</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1899,7 +1570,7 @@
         <v>161</v>
       </c>
       <c r="O32" t="n">
-        <v>22.0296</v>
+        <v>20.7984</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -1908,19 +1579,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>28.4153</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+        <v>27.7314</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>工作城市_规范</t>
@@ -1928,71 +1589,51 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>52</v>
+      </c>
+      <c r="O33" t="n">
+        <v>16.0163</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>27.1987</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>工作城市_规范</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>72</v>
       </c>
-      <c r="O33" t="n">
-        <v>26.1271</v>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O34" t="n">
+        <v>22.7484</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="n">
-        <v>28.1975</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>工作城市_规范</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>46</v>
-      </c>
-      <c r="O34" t="n">
-        <v>25.5944</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>正式主模型在 test 上的分组误差诊断（仅误差诊断，不含敏感属性分析）</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>62.6642</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+        <v>61.9692</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>薪资分位段</t>
@@ -2007,7 +1648,7 @@
         <v>426</v>
       </c>
       <c r="O35" t="n">
-        <v>40.125</v>
+        <v>36.8443</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2016,19 +1657,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>39.6206</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+        <v>38.9929</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>薪资分位段</t>
@@ -2043,7 +1674,7 @@
         <v>474</v>
       </c>
       <c r="O36" t="n">
-        <v>29.2978</v>
+        <v>28.5607</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2052,19 +1683,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>29.2769</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+        <v>29.6516</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>薪资分位段</t>
@@ -2079,7 +1700,7 @@
         <v>464</v>
       </c>
       <c r="O37" t="n">
-        <v>21.378</v>
+        <v>21.9301</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -2088,19 +1709,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>24.2556</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+        <v>23.731</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>薪资分位段</t>
@@ -2115,7 +1726,7 @@
         <v>439</v>
       </c>
       <c r="O38" t="n">
-        <v>18.452</v>
+        <v>17.0952</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2124,19 +1735,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>23.0254</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+        <v>22.8987</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>薪资分位段</t>
@@ -2151,7 +1752,7 @@
         <v>430</v>
       </c>
       <c r="O39" t="n">
-        <v>16.6278</v>
+        <v>15.2992</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2255,7 +1856,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2293,7 +1894,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>15.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2331,7 +1932,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>15.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2369,7 +1970,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2436,13 +2037,13 @@
         <v>320</v>
       </c>
       <c r="C2" t="n">
-        <v>37.947826</v>
+        <v>37.895056</v>
       </c>
       <c r="D2" t="n">
-        <v>74.068512</v>
+        <v>73.830613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.538893</v>
+        <v>0.5418500000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2463,13 +2064,13 @@
         <v>336</v>
       </c>
       <c r="C3" t="n">
-        <v>38.572288</v>
+        <v>38.57584</v>
       </c>
       <c r="D3" t="n">
-        <v>74.96394600000001</v>
+        <v>75.125524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.527676</v>
+        <v>0.525638</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2490,13 +2091,13 @@
         <v>368</v>
       </c>
       <c r="C4" t="n">
-        <v>39.515381</v>
+        <v>39.401318</v>
       </c>
       <c r="D4" t="n">
-        <v>75.668194</v>
+        <v>76.091577</v>
       </c>
       <c r="E4" t="n">
-        <v>0.51876</v>
+        <v>0.51336</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2616,7 +2217,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>按 validation MAE 选出主模型 LightGBM（36.206167）；排序前 3：LightGBM、CatBoost、RandomForest；选择只用 train/validation</t>
+          <t>按 validation MAE 选出主模型 LightGBM（36.088217）；排序前 3：LightGBM、CatBoost、RandomForest；选择只用 train/validation</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2268,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>test 仅在锁定配置后评估一次（n = 2,233，MAE 35.651021），技能阈值/文本维度/超参数/模型族均在 train+validation 上确定，未据 test 调整</t>
+          <t>test 仅在锁定配置后评估一次（n = 2,233，MAE 35.335506），技能阈值/文本维度/超参数/模型族均在 train+validation 上确定，未据 test 调整</t>
         </is>
       </c>
     </row>
@@ -2793,16 +2394,6 @@
           <t>数值列 40，缺失指示 8（缺失列：映射置信度、是否需人工复核、是否跨地域、是否存在同名跨地域歧义、公司规模下限、公司规模上限、公司规模中点、公司规模等级）</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2823,16 +2414,6 @@
           <t>11 个类别字段；训练集频次 ≥ 20 的取值保留，其余并入「__其他__」；缺失编码为「__未知__」</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2853,16 +2434,6 @@
           <t>岗位大类 / 岗位细分类 / 公司认证标签（各自取训练集 Top30）</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2880,19 +2451,9 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>阈值 = 100（train 频率），统计范围 ALL_USABLE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>阈值 = 100（train 频率），口径 ALL_USABLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2913,16 +2474,6 @@
           <t>model-safe BGE 向量在训练集上拟合 TruncatedSVD 后变换</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2943,16 +2494,6 @@
           <t>实际进入模型的特征维度</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2960,8 +2501,6 @@
           <t>技能阈值选择</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>技能频率仅从 train 统计；选择依据仅 validation MAE</t>
@@ -2996,9 +2535,8 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>16.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3006,8 +2544,6 @@
           <t>技能阈值选择</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>技能频率仅从 train 统计；选择依据仅 validation MAE</t>
@@ -3042,9 +2578,8 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3052,8 +2587,6 @@
           <t>技能阈值选择</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>技能频率仅从 train 统计；选择依据仅 validation MAE</t>
@@ -3088,9 +2621,8 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3098,8 +2630,6 @@
           <t>技能阈值选择</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>技能频率仅从 train 统计；选择依据仅 validation MAE</t>
@@ -3134,9 +2664,8 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3144,34 +2673,28 @@
           <t>文本维度选择</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>SVD 仅在 train 上拟合；选择依据仅 validation MAE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>320</v>
       </c>
       <c r="I12" t="n">
-        <v>37.947826</v>
+        <v>37.895056</v>
       </c>
       <c r="J12" t="n">
-        <v>74.068512</v>
+        <v>73.830613</v>
       </c>
       <c r="K12" t="n">
-        <v>0.538893</v>
+        <v>0.5418500000000001</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>RandomForest（固定参数）</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>16</v>
       </c>
@@ -3182,34 +2705,28 @@
           <t>文本维度选择</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>SVD 仅在 train 上拟合；选择依据仅 validation MAE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>336</v>
       </c>
       <c r="I13" t="n">
-        <v>38.572288</v>
+        <v>38.57584</v>
       </c>
       <c r="J13" t="n">
-        <v>74.96394600000001</v>
+        <v>75.125524</v>
       </c>
       <c r="K13" t="n">
-        <v>0.527676</v>
+        <v>0.525638</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>RandomForest（固定参数）</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>32</v>
       </c>
@@ -3220,34 +2737,28 @@
           <t>文本维度选择</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>SVD 仅在 train 上拟合；选择依据仅 validation MAE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>368</v>
       </c>
       <c r="I14" t="n">
-        <v>39.515381</v>
+        <v>39.401318</v>
       </c>
       <c r="J14" t="n">
-        <v>75.668194</v>
+        <v>76.091577</v>
       </c>
       <c r="K14" t="n">
-        <v>0.51876</v>
+        <v>0.51336</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>RandomForest（固定参数）</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>64</v>
       </c>
@@ -3258,16 +2769,11 @@
           <t>文本维度选择</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>仅作参考行，不参与候选选择（正式消融在 Stage 15）</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>304</v>
       </c>
@@ -3285,7 +2791,6 @@
           <t>RandomForest（固定参数）</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>不使用 E 组（参考）</t>
@@ -3432,13 +2937,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.525327</v>
+        <v>45.522012</v>
       </c>
       <c r="D2" t="n">
-        <v>85.262733</v>
+        <v>85.260366</v>
       </c>
       <c r="E2" t="n">
-        <v>0.388983</v>
+        <v>0.389017</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3458,10 +2963,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45.487404</v>
+        <v>45.487769</v>
       </c>
       <c r="D3" t="n">
-        <v>85.26552100000001</v>
+        <v>85.26552</v>
       </c>
       <c r="E3" t="n">
         <v>0.388943</v>
@@ -3484,13 +2989,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45.384395</v>
+        <v>45.385857</v>
       </c>
       <c r="D4" t="n">
-        <v>85.49479599999999</v>
+        <v>85.495599</v>
       </c>
       <c r="E4" t="n">
-        <v>0.385652</v>
+        <v>0.385641</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3510,13 +3015,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.491437</v>
+        <v>45.491613</v>
       </c>
       <c r="D5" t="n">
-        <v>86.86393700000001</v>
+        <v>86.864029</v>
       </c>
       <c r="E5" t="n">
-        <v>0.365818</v>
+        <v>0.365817</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3582,13 +3087,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.947826</v>
+        <v>37.895056</v>
       </c>
       <c r="D2" t="n">
-        <v>74.068512</v>
+        <v>73.830613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.538893</v>
+        <v>0.5418500000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3608,13 +3113,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.526569</v>
+        <v>40.599681</v>
       </c>
       <c r="D3" t="n">
-        <v>79.95421899999999</v>
+        <v>79.94751100000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.462699</v>
+        <v>0.462789</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3634,13 +3139,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.013314</v>
+        <v>38.770234</v>
       </c>
       <c r="D4" t="n">
-        <v>74.564498</v>
+        <v>74.337681</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5326959999999999</v>
+        <v>0.535535</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3660,13 +3165,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.960824</v>
+        <v>40.979075</v>
       </c>
       <c r="D5" t="n">
-        <v>80.26367500000001</v>
+        <v>80.340462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.458532</v>
+        <v>0.457495</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3732,13 +3237,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38.704519</v>
+        <v>38.315285</v>
       </c>
       <c r="D2" t="n">
-        <v>70.436943</v>
+        <v>70.21646200000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.583</v>
+        <v>0.585607</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3758,13 +3263,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.677215</v>
+        <v>36.678336</v>
       </c>
       <c r="D3" t="n">
-        <v>68.938822</v>
+        <v>68.642066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60055</v>
+        <v>0.603981</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3830,13 +3335,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.815171</v>
+        <v>36.95015</v>
       </c>
       <c r="D2" t="n">
-        <v>70.748233</v>
+        <v>70.219453</v>
       </c>
       <c r="E2" t="n">
-        <v>0.579306</v>
+        <v>0.585571</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3856,13 +3361,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="D3" t="n">
-        <v>69.574967</v>
+        <v>69.294882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.593144</v>
+        <v>0.596413</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3882,13 +3387,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.065414</v>
+        <v>37.217811</v>
       </c>
       <c r="D4" t="n">
-        <v>70.757306</v>
+        <v>70.950033</v>
       </c>
       <c r="E4" t="n">
-        <v>0.579198</v>
+        <v>0.5769030000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3964,13 +3469,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="D2" t="n">
-        <v>69.574967</v>
+        <v>69.294882</v>
       </c>
       <c r="E2" t="n">
-        <v>0.593144</v>
+        <v>0.596413</v>
       </c>
       <c r="F2" t="n">
         <v>320</v>
@@ -3998,13 +3503,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.677215</v>
+        <v>36.678336</v>
       </c>
       <c r="D3" t="n">
-        <v>68.938822</v>
+        <v>68.642066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60055</v>
+        <v>0.603981</v>
       </c>
       <c r="F3" t="n">
         <v>320</v>
@@ -4032,13 +3537,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.947826</v>
+        <v>37.895056</v>
       </c>
       <c r="D4" t="n">
-        <v>74.068512</v>
+        <v>73.830613</v>
       </c>
       <c r="E4" t="n">
-        <v>0.538893</v>
+        <v>0.5418500000000001</v>
       </c>
       <c r="F4" t="n">
         <v>320</v>
@@ -4066,13 +3571,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.384395</v>
+        <v>45.385857</v>
       </c>
       <c r="D5" t="n">
-        <v>85.49479599999999</v>
+        <v>85.495599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.385652</v>
+        <v>0.385641</v>
       </c>
       <c r="F5" t="n">
         <v>320</v>
@@ -4180,13 +3685,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.731102</v>
+        <v>43.731547</v>
       </c>
       <c r="C2" t="n">
-        <v>77.230745</v>
+        <v>77.229775</v>
       </c>
       <c r="D2" t="n">
-        <v>0.406719</v>
+        <v>0.406734</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -4209,13 +3714,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.875829</v>
+        <v>36.738923</v>
       </c>
       <c r="C3" t="n">
-        <v>68.322874</v>
+        <v>68.538259</v>
       </c>
       <c r="D3" t="n">
-        <v>0.535686</v>
+        <v>0.532753</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -4238,13 +3743,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.34304</v>
+        <v>36.275629</v>
       </c>
       <c r="C4" t="n">
-        <v>64.751227</v>
+        <v>64.46742399999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.582962</v>
+        <v>0.586609</v>
       </c>
       <c r="E4" t="n">
         <v>2233</v>
@@ -4267,13 +3772,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="C5" t="n">
-        <v>66.191014</v>
+        <v>66.307726</v>
       </c>
       <c r="D5" t="n">
-        <v>0.564209</v>
+        <v>0.562671</v>
       </c>
       <c r="E5" t="n">
         <v>2233</v>
@@ -4325,13 +3830,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.651021</v>
+        <v>35.335506</v>
       </c>
       <c r="C7" t="n">
-        <v>65.020978</v>
+        <v>64.623479</v>
       </c>
       <c r="D7" t="n">
-        <v>0.57948</v>
+        <v>0.584606</v>
       </c>
       <c r="E7" t="n">
         <v>2233</v>
